--- a/salidas/empresas/MS.xlsx
+++ b/salidas/empresas/MS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -431,58 +443,58 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>31.8746452331543</v>
+        <v>31.87463188171387</v>
       </c>
       <c r="C3" t="n">
         <v>59.65999984741211</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>33.56294250488281</v>
+        <v>33.56294631958008</v>
       </c>
       <c r="C4" t="n">
         <v>62.81999969482422</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>34.49876403808594</v>
+        <v>34.498779296875</v>
       </c>
       <c r="C5" t="n">
         <v>64.30000305175781</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>31.98783683776855</v>
+        <v>31.98782348632812</v>
       </c>
       <c r="C6" t="n">
         <v>59.61999893188477</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>33.91394805908203</v>
+        <v>33.91395950317383</v>
       </c>
       <c r="C7" t="n">
         <v>63.20999908447266</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>35.83044815063477</v>
+        <v>35.83045196533203</v>
       </c>
       <c r="C8" t="n">
         <v>66.5</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>35.44789886474609</v>
+        <v>35.44791412353516</v>
       </c>
       <c r="C9" t="n">
         <v>65.79000091552734</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>39.28420257568359</v>
+        <v>39.28418731689453</v>
       </c>
       <c r="C10" t="n">
         <v>72.91000366210938</v>
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>41.18356704711914</v>
+        <v>41.18357467651367</v>
       </c>
       <c r="C12" t="n">
         <v>76.16000366210938</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>44.0333137512207</v>
+        <v>44.0333251953125</v>
       </c>
       <c r="C13" t="n">
         <v>81.43000030517578</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>44.91816329956055</v>
+        <v>44.91819000244141</v>
       </c>
       <c r="C14" t="n">
         <v>82.79000091552734</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>40.64825820922852</v>
+        <v>40.64826965332031</v>
       </c>
       <c r="C15" t="n">
         <v>74.91999816894531</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>42.73167037963867</v>
+        <v>42.73168563842773</v>
       </c>
       <c r="C16" t="n">
         <v>78.76000213623047</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>45.73393249511719</v>
+        <v>45.73390960693359</v>
       </c>
       <c r="C17" t="n">
         <v>84.01000213623047</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>46.29463195800781</v>
+        <v>46.29462051391602</v>
       </c>
       <c r="C18" t="n">
         <v>85.04000091552734</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>45.66313552856445</v>
+        <v>45.66312408447266</v>
       </c>
       <c r="C19" t="n">
         <v>83.87999725341797</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>42.04687118530273</v>
+        <v>42.046875</v>
       </c>
       <c r="C20" t="n">
         <v>63.86999893188477</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>41.05938720703125</v>
+        <v>41.05939483642578</v>
       </c>
       <c r="C21" t="n">
         <v>62.36999893188477</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>41.47414016723633</v>
+        <v>41.47412490844727</v>
       </c>
       <c r="C22" t="n">
         <v>63</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>44.45230102539062</v>
+        <v>44.45229339599609</v>
       </c>
       <c r="C23" t="n">
         <v>67.26000213623047</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>35.10052108764648</v>
+        <v>35.10052490234375</v>
       </c>
       <c r="C25" t="n">
         <v>53.11000061035156</v>
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>28.00014114379883</v>
+        <v>28.0001392364502</v>
       </c>
       <c r="C27" t="n">
         <v>42.11999893188477</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>30.38001823425293</v>
+        <v>30.38003540039062</v>
       </c>
       <c r="C28" t="n">
         <v>45.70000076293945</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>32.49207305908203</v>
+        <v>32.49208068847656</v>
       </c>
       <c r="C29" t="n">
         <v>48.59999847412109</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>29.57045555114746</v>
+        <v>29.57046699523926</v>
       </c>
       <c r="C30" t="n">
         <v>44.22999954223633</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>24.11500358581543</v>
+        <v>24.11500549316406</v>
       </c>
       <c r="C31" t="n">
         <v>36.06999969482422</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>26.5915641784668</v>
+        <v>26.59155082702637</v>
       </c>
       <c r="C32" t="n">
         <v>39.47999954223633</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>27.50084495544434</v>
+        <v>27.5008430480957</v>
       </c>
       <c r="C33" t="n">
         <v>40.83000183105469</v>
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>10.93826961517334</v>
+        <v>10.93827533721924</v>
       </c>
       <c r="C37" t="n">
         <v>16.04000091552734</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>13.98641490936279</v>
+        <v>13.98640823364258</v>
       </c>
       <c r="C38" t="n">
         <v>20.22999954223633</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>13.50936794281006</v>
+        <v>13.50936317443848</v>
       </c>
       <c r="C39" t="n">
         <v>19.54000091552734</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>15.7424898147583</v>
+        <v>15.74248600006104</v>
       </c>
       <c r="C40" t="n">
         <v>22.77000045776367</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>16.39565277099609</v>
+        <v>16.39565467834473</v>
       </c>
       <c r="C41" t="n">
         <v>23.63999938964844</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>21.02859306335449</v>
+        <v>21.02860450744629</v>
       </c>
       <c r="C42" t="n">
         <v>30.31999969482422</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>19.77326393127441</v>
+        <v>19.77326965332031</v>
       </c>
       <c r="C43" t="n">
         <v>28.51000022888184</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>19.80242538452148</v>
+        <v>19.80243301391602</v>
       </c>
       <c r="C44" t="n">
         <v>28.5</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>20.12204742431641</v>
+        <v>20.12204360961914</v>
       </c>
       <c r="C45" t="n">
         <v>28.95999908447266</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>21.45609474182129</v>
+        <v>21.45609664916992</v>
       </c>
       <c r="C46" t="n">
         <v>30.8799991607666</v>
@@ -1349,7 +1361,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>21.97468948364258</v>
+        <v>21.97468566894531</v>
       </c>
       <c r="C48" t="n">
         <v>31.57999992370605</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>20.59692001342773</v>
+        <v>20.59692573547363</v>
       </c>
       <c r="C49" t="n">
         <v>29.60000038146973</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>18.66879844665527</v>
+        <v>18.6688060760498</v>
       </c>
       <c r="C50" t="n">
         <v>26.78000068664551</v>
@@ -1449,7 +1461,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>20.41856575012207</v>
+        <v>20.41856956481934</v>
       </c>
       <c r="C52" t="n">
         <v>29.29000091552734</v>
@@ -1499,7 +1511,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>18.93048477172852</v>
+        <v>18.93046951293945</v>
       </c>
       <c r="C54" t="n">
         <v>27.11000061035156</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>16.20716094970703</v>
+        <v>16.20717239379883</v>
       </c>
       <c r="C55" t="n">
         <v>23.20999908447266</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>18.88164329528809</v>
+        <v>18.88164901733398</v>
       </c>
       <c r="C56" t="n">
         <v>26.98999977111816</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>17.27261352539062</v>
+        <v>17.27262115478516</v>
       </c>
       <c r="C57" t="n">
         <v>24.69000053405762</v>
@@ -1624,7 +1636,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>17.4345760345459</v>
+        <v>17.43457984924316</v>
       </c>
       <c r="C59" t="n">
         <v>24.8700008392334</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>17.14715385437012</v>
+        <v>17.14715194702148</v>
       </c>
       <c r="C60" t="n">
         <v>24.45999908447266</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>19.07499122619629</v>
+        <v>19.07498359680176</v>
       </c>
       <c r="C61" t="n">
         <v>27.20999908447266</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>20.64582443237305</v>
+        <v>20.64581680297852</v>
       </c>
       <c r="C62" t="n">
         <v>29.39999961853027</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>20.84244346618652</v>
+        <v>20.84244155883789</v>
       </c>
       <c r="C63" t="n">
         <v>29.68000030517578</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>19.18515968322754</v>
+        <v>19.18516159057617</v>
       </c>
       <c r="C64" t="n">
         <v>27.31999969482422</v>
@@ -1807,7 +1819,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>16.99896240234375</v>
+        <v>16.99896621704102</v>
       </c>
       <c r="C66" t="n">
         <v>24.15999984741211</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>16.18983268737793</v>
+        <v>16.18982315063477</v>
       </c>
       <c r="C67" t="n">
         <v>23.01000022888184</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>15.68843936920166</v>
+        <v>15.68844699859619</v>
       </c>
       <c r="C68" t="n">
         <v>22.25</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>12.33922576904297</v>
+        <v>12.33922481536865</v>
       </c>
       <c r="C69" t="n">
         <v>17.5</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>9.525882720947266</v>
+        <v>9.525884628295898</v>
       </c>
       <c r="C70" t="n">
         <v>13.51000022888184</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>12.47542381286621</v>
+        <v>12.47541999816895</v>
       </c>
       <c r="C71" t="n">
         <v>17.63999938964844</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>10.4598388671875</v>
+        <v>10.45983791351318</v>
       </c>
       <c r="C72" t="n">
         <v>14.78999996185303</v>
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>10.70029163360596</v>
+        <v>10.70029354095459</v>
       </c>
       <c r="C73" t="n">
         <v>15.13000011444092</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>13.22605991363525</v>
+        <v>13.22605419158936</v>
       </c>
       <c r="C74" t="n">
         <v>18.64999961853027</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>13.14804553985596</v>
+        <v>13.14804649353027</v>
       </c>
       <c r="C75" t="n">
         <v>18.54000091552734</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>13.92813587188721</v>
+        <v>13.92813396453857</v>
       </c>
       <c r="C76" t="n">
         <v>19.63999938964844</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>12.29034328460693</v>
+        <v>12.29033946990967</v>
       </c>
       <c r="C77" t="n">
         <v>17.28000068664551</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>9.502256393432617</v>
+        <v>9.502257347106934</v>
       </c>
       <c r="C78" t="n">
         <v>13.35999965667725</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>10.37708854675293</v>
+        <v>10.37709140777588</v>
       </c>
       <c r="C79" t="n">
         <v>14.59000015258789</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>9.753141403198242</v>
+        <v>9.753143310546875</v>
       </c>
       <c r="C80" t="n">
         <v>13.65999984741211</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>10.70989036560059</v>
+        <v>10.70988941192627</v>
       </c>
       <c r="C81" t="n">
         <v>15</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>11.95223808288574</v>
+        <v>11.95223999023438</v>
       </c>
       <c r="C82" t="n">
         <v>16.73999977111816</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>12.44571399688721</v>
+        <v>12.44571304321289</v>
       </c>
       <c r="C83" t="n">
         <v>17.3799991607666</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>12.08050727844238</v>
+        <v>12.08051013946533</v>
       </c>
       <c r="C84" t="n">
         <v>16.8700008392334</v>
@@ -2385,11 +2397,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>13.69172191619873</v>
+        <v>13.69171714782715</v>
       </c>
       <c r="C85" t="n">
         <v>19.1200008392334</v>
@@ -2412,11 +2424,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>16.36275291442871</v>
+        <v>16.36274909973145</v>
       </c>
       <c r="C86" t="n">
         <v>22.85000038146973</v>
@@ -2439,7 +2451,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2466,11 +2478,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>15.77426433563232</v>
+        <v>15.77426528930664</v>
       </c>
       <c r="C88" t="n">
         <v>21.97999954223633</v>
@@ -2493,11 +2505,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>15.93344688415527</v>
+        <v>15.93344306945801</v>
       </c>
       <c r="C89" t="n">
         <v>22.14999961853027</v>
@@ -2520,11 +2532,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>18.63097763061523</v>
+        <v>18.63097953796387</v>
       </c>
       <c r="C90" t="n">
         <v>25.89999961853027</v>
@@ -2549,7 +2561,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2578,7 +2590,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2607,11 +2619,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>18.56377983093262</v>
+        <v>18.56378173828125</v>
       </c>
       <c r="C93" t="n">
         <v>25.76000022888184</v>
@@ -2636,11 +2648,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>19.42135047912598</v>
+        <v>19.42134475708008</v>
       </c>
       <c r="C94" t="n">
         <v>26.95000076293945</v>
@@ -2665,11 +2677,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>20.73989105224609</v>
+        <v>20.73988723754883</v>
       </c>
       <c r="C95" t="n">
         <v>28.72999954223633</v>
@@ -2694,11 +2706,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>22.59514427185059</v>
+        <v>22.59514045715332</v>
       </c>
       <c r="C96" t="n">
         <v>31.29999923706055</v>
@@ -2723,11 +2735,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>22.63845443725586</v>
+        <v>22.63845825195312</v>
       </c>
       <c r="C97" t="n">
         <v>31.36000061035156</v>
@@ -2752,11 +2764,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>21.33836936950684</v>
+        <v>21.33836555480957</v>
       </c>
       <c r="C98" t="n">
         <v>29.51000022888184</v>
@@ -2781,11 +2793,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>22.27115440368652</v>
+        <v>22.27115821838379</v>
       </c>
       <c r="C99" t="n">
         <v>30.79999923706055</v>
@@ -2810,11 +2822,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>22.5387020111084</v>
+        <v>22.53870391845703</v>
       </c>
       <c r="C100" t="n">
         <v>31.17000007629395</v>
@@ -2839,11 +2851,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>22.43853378295898</v>
+        <v>22.43853187561035</v>
       </c>
       <c r="C101" t="n">
         <v>30.93000030517578</v>
@@ -2868,11 +2880,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>22.38775062561035</v>
+        <v>22.38775253295898</v>
       </c>
       <c r="C102" t="n">
         <v>30.86000061035156</v>
@@ -2897,11 +2909,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>23.45417785644531</v>
+        <v>23.45418548583984</v>
       </c>
       <c r="C103" t="n">
         <v>32.33000183105469</v>
@@ -2926,11 +2938,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>23.53259658813477</v>
+        <v>23.53259468078613</v>
       </c>
       <c r="C104" t="n">
         <v>32.34000015258789</v>
@@ -2955,11 +2967,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>24.96609115600586</v>
+        <v>24.96609306335449</v>
       </c>
       <c r="C105" t="n">
         <v>34.31000137329102</v>
@@ -2984,11 +2996,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>25.1552791595459</v>
+        <v>25.15528678894043</v>
       </c>
       <c r="C106" t="n">
         <v>34.56999969482422</v>
@@ -3013,11 +3025,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>25.50603103637695</v>
+        <v>25.50601768493652</v>
       </c>
       <c r="C107" t="n">
         <v>34.95000076293945</v>
@@ -3042,11 +3054,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>25.67387580871582</v>
+        <v>25.67387390136719</v>
       </c>
       <c r="C108" t="n">
         <v>35.18000030517578</v>
@@ -3071,11 +3083,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>28.31569290161133</v>
+        <v>28.31569671630859</v>
       </c>
       <c r="C109" t="n">
         <v>38.79999923706055</v>
@@ -3100,11 +3112,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>24.74546241760254</v>
+        <v>24.74546051025391</v>
       </c>
       <c r="C110" t="n">
         <v>33.81000137329102</v>
@@ -3129,11 +3141,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>26.19462394714355</v>
+        <v>26.19461441040039</v>
       </c>
       <c r="C111" t="n">
         <v>35.79000091552734</v>
@@ -3158,11 +3170,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>26.12142372131348</v>
+        <v>26.12142181396484</v>
       </c>
       <c r="C112" t="n">
         <v>35.68999862670898</v>
@@ -3187,11 +3199,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>27.41810607910156</v>
+        <v>27.41810989379883</v>
       </c>
       <c r="C113" t="n">
         <v>37.31000137329102</v>
@@ -3216,11 +3228,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>28.07214546203613</v>
+        <v>28.07214736938477</v>
       </c>
       <c r="C114" t="n">
         <v>38.20000076293945</v>
@@ -3245,11 +3257,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>28.50572776794434</v>
+        <v>28.50572204589844</v>
       </c>
       <c r="C115" t="n">
         <v>38.79000091552734</v>
@@ -3274,11 +3286,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>28.65195655822754</v>
+        <v>28.65196418762207</v>
       </c>
       <c r="C116" t="n">
         <v>38.84000015258789</v>
@@ -3303,11 +3315,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>25.41349411010742</v>
+        <v>25.41349601745605</v>
       </c>
       <c r="C117" t="n">
         <v>34.45000076293945</v>
@@ -3332,7 +3344,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3361,11 +3373,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>24.43543243408203</v>
+        <v>24.4354362487793</v>
       </c>
       <c r="C119" t="n">
         <v>32.97000122070312</v>
@@ -3390,11 +3402,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>25.42115211486816</v>
+        <v>25.42115020751953</v>
       </c>
       <c r="C120" t="n">
         <v>34.29999923706055</v>
@@ -3419,7 +3431,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3448,11 +3460,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>19.29427719116211</v>
+        <v>19.29428291320801</v>
       </c>
       <c r="C122" t="n">
         <v>25.8799991607666</v>
@@ -3477,11 +3489,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>18.41456031799316</v>
+        <v>18.41456413269043</v>
       </c>
       <c r="C123" t="n">
         <v>24.70000076293945</v>
@@ -3506,11 +3518,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>18.64566993713379</v>
+        <v>18.64566802978516</v>
       </c>
       <c r="C124" t="n">
         <v>25.01000022888184</v>
@@ -3535,11 +3547,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>20.28444480895996</v>
+        <v>20.28443908691406</v>
       </c>
       <c r="C125" t="n">
         <v>27.05999946594238</v>
@@ -3564,11 +3576,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>20.51682472229004</v>
+        <v>20.5168285369873</v>
       </c>
       <c r="C126" t="n">
         <v>27.3700008392334</v>
@@ -3593,11 +3605,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>19.47486877441406</v>
+        <v>19.47486686706543</v>
       </c>
       <c r="C127" t="n">
         <v>25.97999954223633</v>
@@ -3622,11 +3634,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>21.68467140197754</v>
+        <v>21.6846752166748</v>
       </c>
       <c r="C128" t="n">
         <v>28.72999954223633</v>
@@ -3651,7 +3663,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3680,7 +3692,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3709,11 +3721,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>25.48954200744629</v>
+        <v>25.48954391479492</v>
       </c>
       <c r="C131" t="n">
         <v>33.56999969482422</v>
@@ -3738,11 +3750,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>31.40446281433105</v>
+        <v>31.40445137023926</v>
       </c>
       <c r="C132" t="n">
         <v>41.36000061035156</v>
@@ -3767,7 +3779,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3796,11 +3808,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>32.40970993041992</v>
+        <v>32.40970611572266</v>
       </c>
       <c r="C134" t="n">
         <v>42.4900016784668</v>
@@ -3825,11 +3837,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>34.83527755737305</v>
+        <v>34.83528900146484</v>
       </c>
       <c r="C135" t="n">
         <v>45.66999816894531</v>
@@ -3854,11 +3866,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>32.67667770385742</v>
+        <v>32.67667388916016</v>
       </c>
       <c r="C136" t="n">
         <v>42.84000015258789</v>
@@ -3883,11 +3895,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>33.23071670532227</v>
+        <v>33.23072814941406</v>
       </c>
       <c r="C137" t="n">
         <v>43.36999893188477</v>
@@ -3912,11 +3924,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>31.9817943572998</v>
+        <v>31.98179626464844</v>
       </c>
       <c r="C138" t="n">
         <v>41.7400016784668</v>
@@ -3941,11 +3953,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>34.14252853393555</v>
+        <v>34.14251708984375</v>
       </c>
       <c r="C139" t="n">
         <v>44.56000137329102</v>
@@ -3970,7 +3982,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3999,11 +4011,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>35.04837036132812</v>
+        <v>35.04835510253906</v>
       </c>
       <c r="C141" t="n">
         <v>45.5</v>
@@ -4028,11 +4040,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>37.10504913330078</v>
+        <v>37.10504150390625</v>
       </c>
       <c r="C142" t="n">
         <v>48.16999816894531</v>
@@ -4057,11 +4069,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>38.70380783081055</v>
+        <v>38.70382308959961</v>
       </c>
       <c r="C143" t="n">
         <v>50</v>
@@ -4086,11 +4098,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>39.9500732421875</v>
+        <v>39.95007705688477</v>
       </c>
       <c r="C144" t="n">
         <v>51.61000061035156</v>
@@ -4115,11 +4127,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>40.61577224731445</v>
+        <v>40.61578369140625</v>
       </c>
       <c r="C145" t="n">
         <v>52.47000122070312</v>
@@ -4144,11 +4156,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>43.96533966064453</v>
+        <v>43.96533584594727</v>
       </c>
       <c r="C146" t="n">
         <v>56.54999923706055</v>
@@ -4173,11 +4185,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>43.55327987670898</v>
+        <v>43.55328369140625</v>
       </c>
       <c r="C147" t="n">
         <v>56.02000045776367</v>
@@ -4202,11 +4214,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>41.95170974731445</v>
+        <v>41.95170593261719</v>
       </c>
       <c r="C148" t="n">
         <v>53.95999908447266</v>
@@ -4231,7 +4243,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4260,11 +4272,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>39.16941070556641</v>
+        <v>39.16941452026367</v>
       </c>
       <c r="C150" t="n">
         <v>50.13999938964844</v>
@@ -4289,11 +4301,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>37.02891540527344</v>
+        <v>37.02893447875977</v>
       </c>
       <c r="C151" t="n">
         <v>47.40000152587891</v>
@@ -4318,11 +4330,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>39.73099136352539</v>
+        <v>39.73100280761719</v>
       </c>
       <c r="C152" t="n">
         <v>50.56000137329102</v>
@@ -4347,11 +4359,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>38.37153244018555</v>
+        <v>38.37153625488281</v>
       </c>
       <c r="C153" t="n">
         <v>48.83000183105469</v>
@@ -4376,11 +4388,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>36.5955924987793</v>
+        <v>36.59558868408203</v>
       </c>
       <c r="C154" t="n">
         <v>46.56999969482422</v>
@@ -4405,7 +4417,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4434,11 +4446,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>35.12224197387695</v>
+        <v>35.12223434448242</v>
       </c>
       <c r="C156" t="n">
         <v>44.38999938964844</v>
@@ -4463,11 +4475,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>31.37185668945312</v>
+        <v>31.37186431884766</v>
       </c>
       <c r="C157" t="n">
         <v>39.65000152587891</v>
@@ -4492,7 +4504,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4521,7 +4533,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4550,11 +4562,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>33.62689208984375</v>
+        <v>33.62688827514648</v>
       </c>
       <c r="C160" t="n">
         <v>42.20000076293945</v>
@@ -4579,11 +4591,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>38.6901741027832</v>
+        <v>38.69016647338867</v>
       </c>
       <c r="C161" t="n">
         <v>48.25</v>
@@ -4608,11 +4620,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>32.62804794311523</v>
+        <v>32.6280517578125</v>
       </c>
       <c r="C162" t="n">
         <v>40.68999862670898</v>
@@ -4637,11 +4649,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>35.1298828125</v>
+        <v>35.12986755371094</v>
       </c>
       <c r="C163" t="n">
         <v>43.81000137329102</v>
@@ -4666,7 +4678,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4695,11 +4707,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>33.52899932861328</v>
+        <v>33.52899551391602</v>
       </c>
       <c r="C165" t="n">
         <v>41.4900016784668</v>
@@ -4724,11 +4736,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>34.48257446289062</v>
+        <v>34.48258209228516</v>
       </c>
       <c r="C166" t="n">
         <v>42.66999816894531</v>
@@ -4753,11 +4765,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>37.49425506591797</v>
+        <v>37.49425888061523</v>
       </c>
       <c r="C167" t="n">
         <v>46.04999923706055</v>
@@ -4782,11 +4794,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>40.2869873046875</v>
+        <v>40.2869987487793</v>
       </c>
       <c r="C168" t="n">
         <v>49.47999954223633</v>
@@ -4811,11 +4823,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>41.62229156494141</v>
+        <v>41.62228393554688</v>
       </c>
       <c r="C169" t="n">
         <v>51.11999893188477</v>
@@ -4840,11 +4852,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>42.82974624633789</v>
+        <v>42.82973861694336</v>
       </c>
       <c r="C170" t="n">
         <v>52.2599983215332</v>
@@ -4869,11 +4881,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>36.90438461303711</v>
+        <v>36.90437698364258</v>
       </c>
       <c r="C171" t="n">
         <v>45.02999877929688</v>
@@ -4898,11 +4910,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>27.8647403717041</v>
+        <v>27.86473655700684</v>
       </c>
       <c r="C172" t="n">
         <v>34</v>
@@ -4927,7 +4939,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4956,11 +4968,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>36.54288101196289</v>
+        <v>36.54287719726562</v>
       </c>
       <c r="C174" t="n">
         <v>44.20000076293945</v>
@@ -4985,11 +4997,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>39.93259429931641</v>
+        <v>39.93260955810547</v>
       </c>
       <c r="C175" t="n">
         <v>48.29999923706055</v>
@@ -5014,11 +5026,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>40.69365310668945</v>
+        <v>40.69366073608398</v>
       </c>
       <c r="C176" t="n">
         <v>48.88000106811523</v>
@@ -5043,11 +5055,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>43.5075798034668</v>
+        <v>43.50757598876953</v>
       </c>
       <c r="C177" t="n">
         <v>52.2599983215332</v>
@@ -5072,11 +5084,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>40.25241851806641</v>
+        <v>40.25241470336914</v>
       </c>
       <c r="C178" t="n">
         <v>48.34999847412109</v>
@@ -5101,11 +5113,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>40.38302993774414</v>
+        <v>40.38303375244141</v>
       </c>
       <c r="C179" t="n">
         <v>48.15000152587891</v>
@@ -5130,11 +5142,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>51.85634994506836</v>
+        <v>51.85634613037109</v>
       </c>
       <c r="C180" t="n">
         <v>61.83000183105469</v>
@@ -5159,11 +5171,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>57.47559356689453</v>
+        <v>57.47558212280273</v>
       </c>
       <c r="C181" t="n">
         <v>68.52999877929688</v>
@@ -5188,11 +5200,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>56.52346801757812</v>
+        <v>56.52346420288086</v>
       </c>
       <c r="C182" t="n">
         <v>67.05000305175781</v>
@@ -5217,11 +5229,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>64.80178833007812</v>
+        <v>64.80176544189453</v>
       </c>
       <c r="C183" t="n">
         <v>76.87000274658203</v>
@@ -5246,11 +5258,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>65.46775817871094</v>
+        <v>65.46774291992188</v>
       </c>
       <c r="C184" t="n">
         <v>77.66000366210938</v>
@@ -5275,11 +5287,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>69.88568878173828</v>
+        <v>69.88569641113281</v>
       </c>
       <c r="C185" t="n">
         <v>82.55000305175781</v>
@@ -5304,7 +5316,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5333,11 +5345,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>77.62350463867188</v>
+        <v>77.62351226806641</v>
       </c>
       <c r="C187" t="n">
         <v>91.69000244140625</v>
@@ -5362,7 +5374,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5391,11 +5403,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>89.05789947509766</v>
+        <v>89.05791473388672</v>
       </c>
       <c r="C189" t="n">
         <v>104.4300003051758</v>
@@ -5420,11 +5432,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>82.98597717285156</v>
+        <v>82.98598480224609</v>
       </c>
       <c r="C190" t="n">
         <v>97.30999755859375</v>
@@ -5449,11 +5461,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>88.25724792480469</v>
+        <v>88.25726318359375</v>
       </c>
       <c r="C191" t="n">
         <v>102.7799987792969</v>
@@ -5478,11 +5490,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>81.42200469970703</v>
+        <v>81.42201995849609</v>
       </c>
       <c r="C192" t="n">
         <v>94.81999969482422</v>
@@ -5507,11 +5519,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>84.29005432128906</v>
+        <v>84.29006195068359</v>
       </c>
       <c r="C193" t="n">
         <v>98.16000366210938</v>
@@ -5536,11 +5548,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>88.66477203369141</v>
+        <v>88.66476440429688</v>
       </c>
       <c r="C194" t="n">
         <v>102.5400009155273</v>
@@ -5565,11 +5577,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>78.46146392822266</v>
+        <v>78.46147155761719</v>
       </c>
       <c r="C195" t="n">
         <v>90.73999786376953</v>
@@ -5594,7 +5606,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5623,11 +5635,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>70.28337860107422</v>
+        <v>70.28337097167969</v>
       </c>
       <c r="C197" t="n">
         <v>80.58999633789062</v>
@@ -5652,11 +5664,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>75.12358856201172</v>
+        <v>75.12358093261719</v>
       </c>
       <c r="C198" t="n">
         <v>86.13999938964844</v>
@@ -5681,11 +5693,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>66.33272552490234</v>
+        <v>66.33271789550781</v>
       </c>
       <c r="C199" t="n">
         <v>76.05999755859375</v>
@@ -5710,11 +5722,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>74.21601867675781</v>
+        <v>74.21600341796875</v>
       </c>
       <c r="C200" t="n">
         <v>84.30000305175781</v>
@@ -5739,11 +5751,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>75.02597045898438</v>
+        <v>75.02595520019531</v>
       </c>
       <c r="C201" t="n">
         <v>85.22000122070312</v>
@@ -5768,11 +5780,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>69.55879974365234</v>
+        <v>69.55879211425781</v>
       </c>
       <c r="C202" t="n">
         <v>79.01000213623047</v>
@@ -5797,11 +5809,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>73.04234313964844</v>
+        <v>73.04233551025391</v>
       </c>
       <c r="C203" t="n">
         <v>82.16999816894531</v>
@@ -5826,11 +5838,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>82.73153686523438</v>
+        <v>82.73154449462891</v>
       </c>
       <c r="C204" t="n">
         <v>93.06999969482422</v>
@@ -5855,11 +5867,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>75.57577514648438</v>
+        <v>75.57574462890625</v>
       </c>
       <c r="C205" t="n">
         <v>85.01999664306641</v>
@@ -5884,11 +5896,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>87.2161865234375</v>
+        <v>87.21617126464844</v>
       </c>
       <c r="C206" t="n">
         <v>97.33000183105469</v>
@@ -5913,7 +5925,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5942,7 +5954,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5971,11 +5983,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>81.31920623779297</v>
+        <v>81.31919860839844</v>
       </c>
       <c r="C209" t="n">
         <v>89.97000122070312</v>
@@ -6000,11 +6012,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>73.89861297607422</v>
+        <v>73.89860534667969</v>
       </c>
       <c r="C210" t="n">
         <v>81.76000213623047</v>
@@ -6029,11 +6041,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>77.18861389160156</v>
+        <v>77.18862915039062</v>
       </c>
       <c r="C211" t="n">
         <v>85.40000152587891</v>
@@ -6058,7 +6070,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6087,7 +6099,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6116,11 +6128,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>74.50000762939453</v>
+        <v>74.5</v>
       </c>
       <c r="C214" t="n">
         <v>81.66999816894531</v>
@@ -6145,11 +6157,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>65.39208221435547</v>
+        <v>65.39209747314453</v>
       </c>
       <c r="C215" t="n">
         <v>70.81999969482422</v>
@@ -6174,11 +6186,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>73.25908660888672</v>
+        <v>73.25906372070312</v>
       </c>
       <c r="C216" t="n">
         <v>79.33999633789062</v>
@@ -6203,11 +6215,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>86.10297393798828</v>
+        <v>86.10296630859375</v>
       </c>
       <c r="C217" t="n">
         <v>93.25</v>
@@ -6232,11 +6244,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>81.34270477294922</v>
+        <v>81.34268951416016</v>
       </c>
       <c r="C218" t="n">
         <v>87.23999786376953</v>
@@ -6261,11 +6273,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>80.22382354736328</v>
+        <v>80.22381591796875</v>
       </c>
       <c r="C219" t="n">
         <v>86.04000091552734</v>
@@ -6290,11 +6302,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>87.79491424560547</v>
+        <v>87.794921875</v>
       </c>
       <c r="C220" t="n">
         <v>94.16000366210938</v>
@@ -6319,11 +6331,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>85.4820556640625</v>
+        <v>85.48206329345703</v>
       </c>
       <c r="C221" t="n">
         <v>90.83999633789062</v>
@@ -6348,11 +6360,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>92.06919097900391</v>
+        <v>92.06918334960938</v>
       </c>
       <c r="C222" t="n">
         <v>97.83999633789062</v>
@@ -6377,7 +6389,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6406,11 +6418,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>97.99607086181641</v>
+        <v>97.99607849121094</v>
       </c>
       <c r="C224" t="n">
         <v>103.2099990844727</v>
@@ -6435,7 +6447,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6464,7 +6476,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6493,7 +6505,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6522,11 +6534,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>125.9493560791016</v>
+        <v>125.9493637084961</v>
       </c>
       <c r="C228" t="n">
         <v>131.6100006103516</v>
@@ -6551,11 +6563,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>120.3126907348633</v>
+        <v>120.3126983642578</v>
       </c>
       <c r="C229" t="n">
         <v>125.7200012207031</v>
@@ -6580,7 +6592,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6609,11 +6621,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>128.2324523925781</v>
+        <v>128.2324676513672</v>
       </c>
       <c r="C231" t="n">
         <v>133.1100006103516</v>
@@ -6638,11 +6650,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>112.3948669433594</v>
+        <v>112.3948745727539</v>
       </c>
       <c r="C232" t="n">
         <v>116.6699981689453</v>
@@ -6667,11 +6679,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>112.0828247070312</v>
+        <v>112.0828094482422</v>
       </c>
       <c r="C233" t="n">
         <v>115.4199981689453</v>
@@ -6696,11 +6708,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>124.3282165527344</v>
+        <v>124.3282241821289</v>
       </c>
       <c r="C234" t="n">
         <v>128.0299987792969</v>
@@ -6725,11 +6737,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>136.7872772216797</v>
+        <v>136.7872619628906</v>
       </c>
       <c r="C235" t="n">
         <v>140.8600006103516</v>
@@ -6754,11 +6766,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>139.3021087646484</v>
+        <v>139.3020935058594</v>
       </c>
       <c r="C236" t="n">
         <v>142.4600067138672</v>
@@ -6783,7 +6795,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6812,11 +6824,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>155.4363555908203</v>
+        <v>155.4363708496094</v>
       </c>
       <c r="C238" t="n">
         <v>158.9600067138672</v>
@@ -6841,7 +6853,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6870,7 +6882,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6899,11 +6911,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>174.6515502929688</v>
+        <v>174.6515350341797</v>
       </c>
       <c r="C241" t="n">
         <v>177.5299987792969</v>
@@ -6928,11 +6940,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>180.8274841308594</v>
+        <v>180.8274688720703</v>
       </c>
       <c r="C242" t="n">
         <v>182.8000030517578</v>
@@ -6957,7 +6969,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6986,7 +6998,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7015,7 +7027,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7044,7 +7056,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7073,7 +7085,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7102,7 +7114,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7131,7 +7143,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7160,32 +7172,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>198.3899993896484</v>
+        <v>196.3200073242188</v>
       </c>
       <c r="C250" t="n">
-        <v>198.3899993896484</v>
+        <v>196.3200073242188</v>
       </c>
       <c r="D250" t="n">
-        <v>80939800</v>
+        <v>86135100</v>
       </c>
       <c r="E250" t="n">
         <v>12.37</v>
       </c>
       <c r="F250" t="n">
-        <v>16.0379951002141</v>
+        <v>15.87065540211954</v>
       </c>
       <c r="G250" t="n">
         <v>1570566292</v>
       </c>
       <c r="H250" t="n">
-        <v>311584645711.2824</v>
+        <v>308333585948.6111</v>
       </c>
       <c r="I250" t="n">
-        <v>0.05153542414114157</v>
+        <v>0.05484333927115762</v>
       </c>
     </row>
   </sheetData>
@@ -7217,75 +7229,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7321,13 +7333,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7363,13 +7375,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7405,13 +7417,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7447,13 +7459,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7489,13 +7501,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7522,7 +7534,7 @@
       <c r="I7" t="n">
         <v>-1</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K7" t="n">
@@ -7535,13 +7547,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7568,7 +7580,7 @@
       <c r="I8" t="n">
         <v>0.5599999999999999</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K8" t="n">
@@ -7581,13 +7593,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7614,7 +7626,7 @@
       <c r="I9" t="n">
         <v>2.75</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K9" t="n">
@@ -7627,13 +7639,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7660,7 +7672,7 @@
       <c r="I10" t="n">
         <v>2.3</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K10" t="n">
@@ -7673,13 +7685,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7706,7 +7718,7 @@
       <c r="I11" t="n">
         <v>2.42</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K11" t="n">
@@ -7719,13 +7731,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7752,7 +7764,7 @@
       <c r="I12" t="n">
         <v>1.93</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="K12" t="n">
@@ -7765,13 +7777,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7798,7 +7810,7 @@
       <c r="I13" t="n">
         <v>0.4600000000000002</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="K13" t="n">
@@ -7811,13 +7823,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40854</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7844,7 +7856,7 @@
       <c r="I14" t="n">
         <v>1.68</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40854</v>
       </c>
       <c r="K14" t="n">
@@ -7857,13 +7869,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7890,7 +7902,7 @@
       <c r="I15" t="n">
         <v>1.12</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="K15" t="n">
@@ -7903,13 +7915,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7936,7 +7948,7 @@
       <c r="I16" t="n">
         <v>0.5600000000000002</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="K16" t="n">
@@ -7949,13 +7961,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7982,7 +7994,7 @@
       <c r="I17" t="n">
         <v>1.23</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="K17" t="n">
@@ -7995,13 +8007,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8028,7 +8040,7 @@
       <c r="I18" t="n">
         <v>-0.4699999999999999</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="K18" t="n">
@@ -8041,13 +8053,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8074,7 +8086,7 @@
       <c r="I19" t="n">
         <v>-0.02999999999999986</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="K19" t="n">
@@ -8087,13 +8099,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8120,7 +8132,7 @@
       <c r="I20" t="n">
         <v>0.5100000000000001</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="K20" t="n">
@@ -8133,13 +8145,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8166,7 +8178,7 @@
       <c r="I21" t="n">
         <v>0.6300000000000001</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="K21" t="n">
@@ -8179,13 +8191,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41582</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8212,7 +8224,7 @@
       <c r="I22" t="n">
         <v>1.63</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41582</v>
       </c>
       <c r="K22" t="n">
@@ -8225,13 +8237,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8258,7 +8270,7 @@
       <c r="I23" t="n">
         <v>1.36</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="K23" t="n">
@@ -8271,13 +8283,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8304,7 +8316,7 @@
       <c r="I24" t="n">
         <v>1.62</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="K24" t="n">
@@ -8317,13 +8329,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8350,7 +8362,7 @@
       <c r="I25" t="n">
         <v>2.13</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="K25" t="n">
@@ -8363,13 +8375,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8396,7 +8408,7 @@
       <c r="I26" t="n">
         <v>2.51</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="K26" t="n">
@@ -8409,13 +8421,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8442,7 +8454,7 @@
       <c r="I27" t="n">
         <v>1.58</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="K27" t="n">
@@ -8455,13 +8467,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8488,7 +8500,7 @@
       <c r="I28" t="n">
         <v>2.02</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="K28" t="n">
@@ -8501,13 +8513,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8534,7 +8546,7 @@
       <c r="I29" t="n">
         <v>1.95</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="K29" t="n">
@@ -8547,13 +8559,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8580,7 +8592,7 @@
       <c r="I30" t="n">
         <v>1.6</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="K30" t="n">
@@ -8593,13 +8605,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42423</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8626,7 +8638,7 @@
       <c r="I31" t="n">
         <v>2.9</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42423</v>
       </c>
       <c r="K31" t="n">
@@ -8639,13 +8651,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8672,7 +8684,7 @@
       <c r="I32" t="n">
         <v>2.27</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="K32" t="n">
@@ -8685,13 +8697,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8718,7 +8730,7 @@
       <c r="I33" t="n">
         <v>2.17</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="K33" t="n">
@@ -8731,13 +8743,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8764,7 +8776,7 @@
       <c r="I34" t="n">
         <v>2.5</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="K34" t="n">
@@ -8777,13 +8789,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8810,7 +8822,7 @@
       <c r="I35" t="n">
         <v>2.920000000000001</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="K35" t="n">
@@ -8823,13 +8835,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8856,7 +8868,7 @@
       <c r="I36" t="n">
         <v>3.37</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="K36" t="n">
@@ -8869,13 +8881,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8902,7 +8914,7 @@
       <c r="I37" t="n">
         <v>3.49</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="K37" t="n">
@@ -8915,13 +8927,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8948,7 +8960,7 @@
       <c r="I38" t="n">
         <v>3.61</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="K38" t="n">
@@ -8961,13 +8973,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8994,7 +9006,7 @@
       <c r="I39" t="n">
         <v>3.06</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="K39" t="n">
@@ -9007,13 +9019,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9040,7 +9052,7 @@
       <c r="I40" t="n">
         <v>3.51</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="K40" t="n">
@@ -9053,13 +9065,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9086,7 +9098,7 @@
       <c r="I41" t="n">
         <v>3.94</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="K41" t="n">
@@ -9099,13 +9111,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9132,7 +9144,7 @@
       <c r="I42" t="n">
         <v>4.180000000000001</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="K42" t="n">
@@ -9145,13 +9157,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9178,7 +9190,7 @@
       <c r="I43" t="n">
         <v>4.720000000000001</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="K43" t="n">
@@ -9191,13 +9203,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9224,7 +9236,7 @@
       <c r="I44" t="n">
         <v>4.66</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="K44" t="n">
@@ -9237,13 +9249,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43682</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9270,7 +9282,7 @@
       <c r="I45" t="n">
         <v>4.59</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43682</v>
       </c>
       <c r="K45" t="n">
@@ -9283,13 +9295,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9316,7 +9328,7 @@
       <c r="I46" t="n">
         <v>4.69</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="K46" t="n">
@@ -9329,13 +9341,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9362,7 +9374,7 @@
       <c r="I47" t="n">
         <v>5.19</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="K47" t="n">
@@ -9375,13 +9387,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9408,7 +9420,7 @@
       <c r="I48" t="n">
         <v>4.81</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="K48" t="n">
@@ -9421,13 +9433,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9454,7 +9466,7 @@
       <c r="I49" t="n">
         <v>5.54</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="K49" t="n">
@@ -9467,13 +9479,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9500,7 +9512,7 @@
       <c r="I50" t="n">
         <v>5.93</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="K50" t="n">
@@ -9513,13 +9525,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9546,7 +9558,7 @@
       <c r="I51" t="n">
         <v>6.44</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="K51" t="n">
@@ -9559,13 +9571,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44319</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9592,7 +9604,7 @@
       <c r="I52" t="n">
         <v>7.62</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44319</v>
       </c>
       <c r="K52" t="n">
@@ -9605,13 +9617,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44410</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9638,7 +9650,7 @@
       <c r="I53" t="n">
         <v>7.51</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44410</v>
       </c>
       <c r="K53" t="n">
@@ -9651,13 +9663,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9684,7 +9696,7 @@
       <c r="I54" t="n">
         <v>7.83</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="K54" t="n">
@@ -9697,13 +9709,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9730,7 +9742,7 @@
       <c r="I55" t="n">
         <v>8.030000000000001</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="K55" t="n">
@@ -9743,13 +9755,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9776,7 +9788,7 @@
       <c r="I56" t="n">
         <v>7.859999999999999</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="K56" t="n">
@@ -9789,13 +9801,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9822,7 +9834,7 @@
       <c r="I57" t="n">
         <v>7.4</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="K57" t="n">
@@ -9835,13 +9847,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9868,7 +9880,7 @@
       <c r="I58" t="n">
         <v>6.89</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K58" t="n">
@@ -9881,13 +9893,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9914,7 +9926,7 @@
       <c r="I59" t="n">
         <v>6.15</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="K59" t="n">
@@ -9927,13 +9939,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9960,7 +9972,7 @@
       <c r="I60" t="n">
         <v>5.830000000000001</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="K60" t="n">
@@ -9973,13 +9985,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10006,7 +10018,7 @@
       <c r="I61" t="n">
         <v>5.68</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K61" t="n">
@@ -10019,13 +10031,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10052,7 +10064,7 @@
       <c r="I62" t="n">
         <v>5.59</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="K62" t="n">
@@ -10065,13 +10077,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10098,7 +10110,7 @@
       <c r="I63" t="n">
         <v>5.18</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="K63" t="n">
@@ -10111,13 +10123,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10144,7 +10156,7 @@
       <c r="I64" t="n">
         <v>5.499999999999999</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="K64" t="n">
@@ -10157,13 +10169,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10190,7 +10202,7 @@
       <c r="I65" t="n">
         <v>6.08</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="K65" t="n">
@@ -10203,13 +10215,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10236,7 +10248,7 @@
       <c r="I66" t="n">
         <v>6.579999999999999</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="K66" t="n">
@@ -10249,13 +10261,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10282,7 +10294,7 @@
       <c r="I67" t="n">
         <v>7.950000000000001</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="K67" t="n">
@@ -10295,13 +10307,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10328,7 +10340,7 @@
       <c r="I68" t="n">
         <v>8.530000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="K68" t="n">
@@ -10341,13 +10353,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10374,7 +10386,7 @@
       <c r="I69" t="n">
         <v>8.84</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="K69" t="n">
@@ -10387,13 +10399,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10420,7 +10432,7 @@
       <c r="I70" t="n">
         <v>9.76</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="K70" t="n">
@@ -10433,13 +10445,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10466,7 +10478,7 @@
       <c r="I71" t="n">
         <v>10.21</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="K71" t="n">
@@ -10479,13 +10491,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10512,7 +10524,7 @@
       <c r="I72" t="n">
         <v>11.04</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="K72" t="n">
@@ -10525,13 +10537,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10558,7 +10570,7 @@
       <c r="I73" t="n">
         <v>12.37</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="K73" t="n">
@@ -10595,52 +10607,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="C2" t="n">
@@ -10669,10 +10681,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="C3" t="n">
@@ -10701,10 +10713,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10733,10 +10745,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C5" t="n">
@@ -10765,10 +10777,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="C6" t="n">
@@ -10797,10 +10809,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="C7" t="n">
@@ -10829,10 +10841,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="C8" t="n">
@@ -10861,10 +10873,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40672</v>
       </c>
       <c r="C9" t="n">
@@ -10893,10 +10905,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="C10" t="n">
@@ -10925,10 +10937,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40854</v>
       </c>
       <c r="C11" t="n">
@@ -10957,10 +10969,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="C12" t="n">
@@ -10989,10 +11001,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="C13" t="n">
@@ -11021,10 +11033,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41127</v>
       </c>
       <c r="C14" t="n">
@@ -11053,10 +11065,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="C15" t="n">
@@ -11085,10 +11097,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41310</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41331</v>
       </c>
       <c r="C16" t="n">
@@ -11117,10 +11129,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="C17" t="n">
@@ -11149,10 +11161,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="C18" t="n">
@@ -11181,10 +11193,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41582</v>
       </c>
       <c r="C19" t="n">
@@ -11213,10 +11225,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="C20" t="n">
@@ -11245,10 +11257,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="C21" t="n">
@@ -11277,10 +11289,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="C22" t="n">
@@ -11309,10 +11321,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="C23" t="n">
@@ -11341,10 +11353,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42065</v>
       </c>
       <c r="C24" t="n">
@@ -11373,10 +11385,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42128</v>
       </c>
       <c r="C25" t="n">
@@ -11405,10 +11417,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="C26" t="n">
@@ -11437,10 +11449,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42307</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="C27" t="n">
@@ -11469,10 +11481,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42423</v>
       </c>
       <c r="C28" t="n">
@@ -11501,10 +11513,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="C29" t="n">
@@ -11533,10 +11545,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="C30" t="n">
@@ -11565,10 +11577,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42676</v>
       </c>
       <c r="C31" t="n">
@@ -11597,10 +11609,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42793</v>
       </c>
       <c r="C32" t="n">
@@ -11629,10 +11641,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42856</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C33" t="n">
@@ -11661,10 +11673,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="C34" t="n">
@@ -11693,10 +11705,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="C35" t="n">
@@ -11725,10 +11737,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43158</v>
       </c>
       <c r="C36" t="n">
@@ -11757,10 +11769,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="C37" t="n">
@@ -11789,10 +11801,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="C38" t="n">
@@ -11821,10 +11833,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="C39" t="n">
@@ -11853,10 +11865,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="C40" t="n">
@@ -11885,10 +11897,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="C41" t="n">
@@ -11917,10 +11929,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43682</v>
       </c>
       <c r="C42" t="n">
@@ -11949,10 +11961,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="C43" t="n">
@@ -11981,10 +11993,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="C44" t="n">
@@ -12013,10 +12025,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="C45" t="n">
@@ -12045,10 +12057,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="C46" t="n">
@@ -12077,10 +12089,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44134</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="C47" t="n">
@@ -12109,10 +12121,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="C48" t="n">
@@ -12141,10 +12153,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44319</v>
       </c>
       <c r="C49" t="n">
@@ -12173,10 +12185,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44407</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44410</v>
       </c>
       <c r="C50" t="n">
@@ -12205,10 +12217,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44503</v>
       </c>
       <c r="C51" t="n">
@@ -12237,10 +12249,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44616</v>
       </c>
       <c r="C52" t="n">
@@ -12269,10 +12281,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44680</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="C53" t="n">
@@ -12301,10 +12313,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44771</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="C54" t="n">
@@ -12333,10 +12345,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C55" t="n">
@@ -12365,10 +12377,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="C56" t="n">
@@ -12397,10 +12409,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="C57" t="n">
@@ -12429,10 +12441,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C58" t="n">
@@ -12461,10 +12473,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="C59" t="n">
@@ -12493,10 +12505,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="C60" t="n">
@@ -12525,10 +12537,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="C61" t="n">
@@ -12557,10 +12569,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45509</v>
       </c>
       <c r="C62" t="n">
@@ -12589,10 +12601,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="C63" t="n">
@@ -12621,10 +12633,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="C64" t="n">
@@ -12653,10 +12665,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45782</v>
       </c>
       <c r="C65" t="n">
@@ -12685,10 +12697,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45873</v>
       </c>
       <c r="C66" t="n">
@@ -12717,10 +12729,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="C67" t="n">
@@ -12749,10 +12761,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46072</v>
       </c>
       <c r="C68" t="n">
@@ -12781,10 +12793,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46147</v>
       </c>
       <c r="C69" t="n">
@@ -12813,10 +12825,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46238</v>
       </c>
       <c r="C70" t="n">
@@ -12863,12 +12875,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/MS.xlsx
+++ b/salidas/empresas/MS.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>32.83098220825195</v>
+        <v>32.83097839355469</v>
       </c>
       <c r="C2" t="n">
         <v>61.45000076293945</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>31.87463188171387</v>
+        <v>31.8746452331543</v>
       </c>
       <c r="C3" t="n">
         <v>59.65999984741211</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>33.56294631958008</v>
+        <v>33.56292724609375</v>
       </c>
       <c r="C4" t="n">
         <v>62.81999969482422</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>34.498779296875</v>
+        <v>34.49878311157227</v>
       </c>
       <c r="C5" t="n">
         <v>64.30000305175781</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>31.98782348632812</v>
+        <v>31.98780822753906</v>
       </c>
       <c r="C6" t="n">
         <v>59.61999893188477</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>33.91395950317383</v>
+        <v>33.91394424438477</v>
       </c>
       <c r="C7" t="n">
         <v>63.20999908447266</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>35.83045196533203</v>
+        <v>35.83046722412109</v>
       </c>
       <c r="C8" t="n">
         <v>66.5</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>35.44791412353516</v>
+        <v>35.44790649414062</v>
       </c>
       <c r="C9" t="n">
         <v>65.79000091552734</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>39.28418731689453</v>
+        <v>39.28419876098633</v>
       </c>
       <c r="C10" t="n">
         <v>72.91000366210938</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>41.32957077026367</v>
+        <v>41.32956314086914</v>
       </c>
       <c r="C11" t="n">
         <v>76.43000030517578</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>44.0333251953125</v>
+        <v>44.03331756591797</v>
       </c>
       <c r="C13" t="n">
         <v>81.43000030517578</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>44.91819000244141</v>
+        <v>44.91818618774414</v>
       </c>
       <c r="C14" t="n">
         <v>82.79000091552734</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>40.64826965332031</v>
+        <v>40.64826202392578</v>
       </c>
       <c r="C15" t="n">
         <v>74.91999816894531</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>42.73168563842773</v>
+        <v>42.73166656494141</v>
       </c>
       <c r="C16" t="n">
         <v>78.76000213623047</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>45.73390960693359</v>
+        <v>45.73390579223633</v>
       </c>
       <c r="C17" t="n">
         <v>84.01000213623047</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>46.29462051391602</v>
+        <v>46.29463958740234</v>
       </c>
       <c r="C18" t="n">
         <v>85.04000091552734</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>45.66312408447266</v>
+        <v>45.66313934326172</v>
       </c>
       <c r="C19" t="n">
         <v>83.87999725341797</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>42.046875</v>
+        <v>42.0468635559082</v>
       </c>
       <c r="C20" t="n">
         <v>63.86999893188477</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>41.05939483642578</v>
+        <v>41.05938339233398</v>
       </c>
       <c r="C21" t="n">
         <v>62.36999893188477</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>41.47412490844727</v>
+        <v>41.47415542602539</v>
       </c>
       <c r="C22" t="n">
         <v>63</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>44.45229339599609</v>
+        <v>44.4522819519043</v>
       </c>
       <c r="C23" t="n">
         <v>67.26000213623047</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>35.10052490234375</v>
+        <v>35.10051727294922</v>
       </c>
       <c r="C25" t="n">
         <v>53.11000061035156</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>32.79978561401367</v>
+        <v>32.79977035522461</v>
       </c>
       <c r="C26" t="n">
         <v>49.34000015258789</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>28.0001392364502</v>
+        <v>28.0001335144043</v>
       </c>
       <c r="C27" t="n">
         <v>42.11999893188477</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>30.38003540039062</v>
+        <v>30.3800163269043</v>
       </c>
       <c r="C28" t="n">
         <v>45.70000076293945</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>29.57046699523926</v>
+        <v>29.57047843933105</v>
       </c>
       <c r="C30" t="n">
         <v>44.22999954223633</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>24.11500549316406</v>
+        <v>24.11500930786133</v>
       </c>
       <c r="C31" t="n">
         <v>36.06999969482422</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>26.59155082702637</v>
+        <v>26.591552734375</v>
       </c>
       <c r="C32" t="n">
         <v>39.47999954223633</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>27.5008430480957</v>
+        <v>27.50085067749023</v>
       </c>
       <c r="C33" t="n">
         <v>40.83000183105469</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>15.49153900146484</v>
+        <v>15.49153518676758</v>
       </c>
       <c r="C34" t="n">
         <v>23</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>11.91344261169434</v>
+        <v>11.9134407043457</v>
       </c>
       <c r="C35" t="n">
         <v>17.46999931335449</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>10.05857372283936</v>
+        <v>10.05857563018799</v>
       </c>
       <c r="C36" t="n">
         <v>14.75</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>10.93827533721924</v>
+        <v>10.93827438354492</v>
       </c>
       <c r="C37" t="n">
         <v>16.04000091552734</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>13.98640823364258</v>
+        <v>13.98641014099121</v>
       </c>
       <c r="C38" t="n">
         <v>20.22999954223633</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>13.50936317443848</v>
+        <v>13.50936222076416</v>
       </c>
       <c r="C39" t="n">
         <v>19.54000091552734</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>15.74248600006104</v>
+        <v>15.7424898147583</v>
       </c>
       <c r="C40" t="n">
         <v>22.77000045776367</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>16.39565467834473</v>
+        <v>16.3956470489502</v>
       </c>
       <c r="C41" t="n">
         <v>23.63999938964844</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>19.80243301391602</v>
+        <v>19.80242919921875</v>
       </c>
       <c r="C44" t="n">
         <v>28.5</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>20.12204360961914</v>
+        <v>20.12204170227051</v>
       </c>
       <c r="C45" t="n">
         <v>28.95999908447266</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>21.45609664916992</v>
+        <v>21.45610237121582</v>
       </c>
       <c r="C46" t="n">
         <v>30.8799991607666</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>22.35044097900391</v>
+        <v>22.35045051574707</v>
       </c>
       <c r="C47" t="n">
         <v>32.11999893188477</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>21.97468566894531</v>
+        <v>21.97468757629395</v>
       </c>
       <c r="C48" t="n">
         <v>31.57999992370605</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>20.59692573547363</v>
+        <v>20.59692001342773</v>
       </c>
       <c r="C49" t="n">
         <v>29.60000038146973</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>18.6688060760498</v>
+        <v>18.66880226135254</v>
       </c>
       <c r="C50" t="n">
         <v>26.78000068664551</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>19.64477157592773</v>
+        <v>19.64476776123047</v>
       </c>
       <c r="C51" t="n">
         <v>28.18000030517578</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>20.41856956481934</v>
+        <v>20.41857719421387</v>
       </c>
       <c r="C52" t="n">
         <v>29.29000091552734</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>21.10214233398438</v>
+        <v>21.10213470458984</v>
       </c>
       <c r="C53" t="n">
         <v>30.21999931335449</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>18.93046951293945</v>
+        <v>18.93048286437988</v>
       </c>
       <c r="C54" t="n">
         <v>27.11000061035156</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>17.2656192779541</v>
+        <v>17.26561737060547</v>
       </c>
       <c r="C58" t="n">
         <v>24.68000030517578</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>17.43457984924316</v>
+        <v>17.4345760345459</v>
       </c>
       <c r="C59" t="n">
         <v>24.8700008392334</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>17.14715194702148</v>
+        <v>17.14715576171875</v>
       </c>
       <c r="C60" t="n">
         <v>24.45999908447266</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>19.07498359680176</v>
+        <v>19.07497978210449</v>
       </c>
       <c r="C61" t="n">
         <v>27.20999908447266</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>20.84244155883789</v>
+        <v>20.84244728088379</v>
       </c>
       <c r="C63" t="n">
         <v>29.68000030517578</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>19.18516159057617</v>
+        <v>19.18516540527344</v>
       </c>
       <c r="C64" t="n">
         <v>27.31999969482422</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>16.99896621704102</v>
+        <v>16.99896049499512</v>
       </c>
       <c r="C66" t="n">
         <v>24.15999984741211</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>16.18982315063477</v>
+        <v>16.18982696533203</v>
       </c>
       <c r="C67" t="n">
         <v>23.01000022888184</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>15.68844699859619</v>
+        <v>15.68844985961914</v>
       </c>
       <c r="C68" t="n">
         <v>22.25</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>12.33922481536865</v>
+        <v>12.3392276763916</v>
       </c>
       <c r="C69" t="n">
         <v>17.5</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>9.525884628295898</v>
+        <v>9.525883674621582</v>
       </c>
       <c r="C70" t="n">
         <v>13.51000022888184</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>12.47541999816895</v>
+        <v>12.47542476654053</v>
       </c>
       <c r="C71" t="n">
         <v>17.63999938964844</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>10.70029354095459</v>
+        <v>10.70029640197754</v>
       </c>
       <c r="C73" t="n">
         <v>15.13000011444092</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>13.22605419158936</v>
+        <v>13.22605228424072</v>
       </c>
       <c r="C74" t="n">
         <v>18.64999961853027</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>13.14804649353027</v>
+        <v>13.14804744720459</v>
       </c>
       <c r="C75" t="n">
         <v>18.54000091552734</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>13.92813396453857</v>
+        <v>13.92813587188721</v>
       </c>
       <c r="C76" t="n">
         <v>19.63999938964844</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>12.29033946990967</v>
+        <v>12.29034423828125</v>
       </c>
       <c r="C77" t="n">
         <v>17.28000068664551</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>9.502257347106934</v>
+        <v>9.502255439758301</v>
       </c>
       <c r="C78" t="n">
         <v>13.35999965667725</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>9.753143310546875</v>
+        <v>9.753141403198242</v>
       </c>
       <c r="C80" t="n">
         <v>13.65999984741211</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>10.70988941192627</v>
+        <v>10.70989418029785</v>
       </c>
       <c r="C81" t="n">
         <v>15</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>11.95223999023438</v>
+        <v>11.95224189758301</v>
       </c>
       <c r="C82" t="n">
         <v>16.73999977111816</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>12.44571304321289</v>
+        <v>12.44571590423584</v>
       </c>
       <c r="C83" t="n">
         <v>17.3799991607666</v>
@@ -2401,7 +2401,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>13.69171714782715</v>
+        <v>13.6917200088501</v>
       </c>
       <c r="C85" t="n">
         <v>19.1200008392334</v>
@@ -2428,7 +2428,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>16.36274909973145</v>
+        <v>16.36275100708008</v>
       </c>
       <c r="C86" t="n">
         <v>22.85000038146973</v>
@@ -2455,7 +2455,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>16.1833381652832</v>
+        <v>16.1833324432373</v>
       </c>
       <c r="C87" t="n">
         <v>22.54999923706055</v>
@@ -2482,7 +2482,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>15.77426528930664</v>
+        <v>15.77426242828369</v>
       </c>
       <c r="C88" t="n">
         <v>21.97999954223633</v>
@@ -2509,7 +2509,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>15.93344306945801</v>
+        <v>15.93345165252686</v>
       </c>
       <c r="C89" t="n">
         <v>22.14999961853027</v>
@@ -2565,7 +2565,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>17.57354545593262</v>
+        <v>17.57353973388672</v>
       </c>
       <c r="C91" t="n">
         <v>24.43000030517578</v>
@@ -2594,7 +2594,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>19.60871315002441</v>
+        <v>19.60871124267578</v>
       </c>
       <c r="C92" t="n">
         <v>27.20999908447266</v>
@@ -2652,7 +2652,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>19.42134475708008</v>
+        <v>19.42134857177734</v>
       </c>
       <c r="C94" t="n">
         <v>26.95000076293945</v>
@@ -2710,7 +2710,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>22.59514045715332</v>
+        <v>22.59514617919922</v>
       </c>
       <c r="C96" t="n">
         <v>31.29999923706055</v>
@@ -2739,7 +2739,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>22.63845825195312</v>
+        <v>22.63846015930176</v>
       </c>
       <c r="C97" t="n">
         <v>31.36000061035156</v>
@@ -2768,7 +2768,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>21.33836555480957</v>
+        <v>21.33837127685547</v>
       </c>
       <c r="C98" t="n">
         <v>29.51000022888184</v>
@@ -2797,7 +2797,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>22.27115821838379</v>
+        <v>22.27115249633789</v>
       </c>
       <c r="C99" t="n">
         <v>30.79999923706055</v>
@@ -2826,7 +2826,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>22.53870391845703</v>
+        <v>22.53870010375977</v>
       </c>
       <c r="C100" t="n">
         <v>31.17000007629395</v>
@@ -2884,7 +2884,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>22.38775253295898</v>
+        <v>22.38775062561035</v>
       </c>
       <c r="C102" t="n">
         <v>30.86000061035156</v>
@@ -2942,7 +2942,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>23.53259468078613</v>
+        <v>23.53260040283203</v>
       </c>
       <c r="C104" t="n">
         <v>32.34000015258789</v>
@@ -2971,7 +2971,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>24.96609306335449</v>
+        <v>24.96609115600586</v>
       </c>
       <c r="C105" t="n">
         <v>34.31000137329102</v>
@@ -3000,7 +3000,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>25.15528678894043</v>
+        <v>25.15527534484863</v>
       </c>
       <c r="C106" t="n">
         <v>34.56999969482422</v>
@@ -3029,7 +3029,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>25.50601768493652</v>
+        <v>25.50602531433105</v>
       </c>
       <c r="C107" t="n">
         <v>34.95000076293945</v>
@@ -3058,7 +3058,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>25.67387390136719</v>
+        <v>25.67387771606445</v>
       </c>
       <c r="C108" t="n">
         <v>35.18000030517578</v>
@@ -3087,7 +3087,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>28.31569671630859</v>
+        <v>28.31570243835449</v>
       </c>
       <c r="C109" t="n">
         <v>38.79999923706055</v>
@@ -3116,7 +3116,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>24.74546051025391</v>
+        <v>24.74546241760254</v>
       </c>
       <c r="C110" t="n">
         <v>33.81000137329102</v>
@@ -3145,7 +3145,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>26.19461441040039</v>
+        <v>26.19462776184082</v>
       </c>
       <c r="C111" t="n">
         <v>35.79000091552734</v>
@@ -3174,7 +3174,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>26.12142181396484</v>
+        <v>26.12143325805664</v>
       </c>
       <c r="C112" t="n">
         <v>35.68999862670898</v>
@@ -3203,7 +3203,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>27.41810989379883</v>
+        <v>27.41810607910156</v>
       </c>
       <c r="C113" t="n">
         <v>37.31000137329102</v>
@@ -3232,7 +3232,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>28.07214736938477</v>
+        <v>28.07215118408203</v>
       </c>
       <c r="C114" t="n">
         <v>38.20000076293945</v>
@@ -3261,7 +3261,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>28.50572204589844</v>
+        <v>28.50571250915527</v>
       </c>
       <c r="C115" t="n">
         <v>38.79000091552734</v>
@@ -3290,7 +3290,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>28.65196418762207</v>
+        <v>28.65196800231934</v>
       </c>
       <c r="C116" t="n">
         <v>38.84000015258789</v>
@@ -3319,7 +3319,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>25.41349601745605</v>
+        <v>25.41349411010742</v>
       </c>
       <c r="C117" t="n">
         <v>34.45000076293945</v>
@@ -3348,7 +3348,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>23.2372989654541</v>
+        <v>23.23730659484863</v>
       </c>
       <c r="C118" t="n">
         <v>31.5</v>
@@ -3377,7 +3377,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>24.4354362487793</v>
+        <v>24.43543815612793</v>
       </c>
       <c r="C119" t="n">
         <v>32.97000122070312</v>
@@ -3406,7 +3406,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>25.42115020751953</v>
+        <v>25.4211483001709</v>
       </c>
       <c r="C120" t="n">
         <v>34.29999923706055</v>
@@ -3435,7 +3435,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>23.57570648193359</v>
+        <v>23.57570838928223</v>
       </c>
       <c r="C121" t="n">
         <v>31.80999946594238</v>
@@ -3464,7 +3464,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>19.29428291320801</v>
+        <v>19.29428100585938</v>
       </c>
       <c r="C122" t="n">
         <v>25.8799991607666</v>
@@ -3493,7 +3493,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>18.41456413269043</v>
+        <v>18.41455841064453</v>
       </c>
       <c r="C123" t="n">
         <v>24.70000076293945</v>
@@ -3522,7 +3522,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>18.64566802978516</v>
+        <v>18.64567375183105</v>
       </c>
       <c r="C124" t="n">
         <v>25.01000022888184</v>
@@ -3551,7 +3551,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>20.28443908691406</v>
+        <v>20.28444862365723</v>
       </c>
       <c r="C125" t="n">
         <v>27.05999946594238</v>
@@ -3580,7 +3580,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>20.5168285369873</v>
+        <v>20.51683044433594</v>
       </c>
       <c r="C126" t="n">
         <v>27.3700008392334</v>
@@ -3609,7 +3609,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>19.47486686706543</v>
+        <v>19.47486877441406</v>
       </c>
       <c r="C127" t="n">
         <v>25.97999954223633</v>
@@ -3638,7 +3638,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>21.6846752166748</v>
+        <v>21.68466949462891</v>
       </c>
       <c r="C128" t="n">
         <v>28.72999954223633</v>
@@ -3667,7 +3667,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>24.19807052612305</v>
+        <v>24.19806861877441</v>
       </c>
       <c r="C129" t="n">
         <v>32.06000137329102</v>
@@ -3696,7 +3696,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>24.19807052612305</v>
+        <v>24.19806861877441</v>
       </c>
       <c r="C130" t="n">
         <v>32.06000137329102</v>
@@ -3725,7 +3725,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>25.48954391479492</v>
+        <v>25.48954772949219</v>
       </c>
       <c r="C131" t="n">
         <v>33.56999969482422</v>
@@ -3754,7 +3754,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>31.40445137023926</v>
+        <v>31.40445327758789</v>
       </c>
       <c r="C132" t="n">
         <v>41.36000061035156</v>
@@ -3783,7 +3783,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>32.08023452758789</v>
+        <v>32.08023834228516</v>
       </c>
       <c r="C133" t="n">
         <v>42.25</v>
@@ -3841,7 +3841,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>34.83528900146484</v>
+        <v>34.83527755737305</v>
       </c>
       <c r="C135" t="n">
         <v>45.66999816894531</v>
@@ -3870,7 +3870,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>32.67667388916016</v>
+        <v>32.67668151855469</v>
       </c>
       <c r="C136" t="n">
         <v>42.84000015258789</v>
@@ -3899,7 +3899,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>33.23072814941406</v>
+        <v>33.23071670532227</v>
       </c>
       <c r="C137" t="n">
         <v>43.36999893188477</v>
@@ -3928,7 +3928,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>31.98179626464844</v>
+        <v>31.9818000793457</v>
       </c>
       <c r="C138" t="n">
         <v>41.7400016784668</v>
@@ -3957,7 +3957,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>34.14251708984375</v>
+        <v>34.14252853393555</v>
       </c>
       <c r="C139" t="n">
         <v>44.56000137329102</v>
@@ -3986,7 +3986,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>36.12677764892578</v>
+        <v>36.12675476074219</v>
       </c>
       <c r="C140" t="n">
         <v>46.90000152587891</v>
@@ -4015,7 +4015,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>35.04835510253906</v>
+        <v>35.04835891723633</v>
       </c>
       <c r="C141" t="n">
         <v>45.5</v>
@@ -4044,7 +4044,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>37.10504150390625</v>
+        <v>37.10504913330078</v>
       </c>
       <c r="C142" t="n">
         <v>48.16999816894531</v>
@@ -4073,7 +4073,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>38.70382308959961</v>
+        <v>38.70381164550781</v>
       </c>
       <c r="C143" t="n">
         <v>50</v>
@@ -4102,7 +4102,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>39.95007705688477</v>
+        <v>39.95006942749023</v>
       </c>
       <c r="C144" t="n">
         <v>51.61000061035156</v>
@@ -4131,7 +4131,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>40.61578369140625</v>
+        <v>40.61577606201172</v>
       </c>
       <c r="C145" t="n">
         <v>52.47000122070312</v>
@@ -4160,7 +4160,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>43.96533584594727</v>
+        <v>43.96533203125</v>
       </c>
       <c r="C146" t="n">
         <v>56.54999923706055</v>
@@ -4218,7 +4218,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>41.95170593261719</v>
+        <v>41.95171737670898</v>
       </c>
       <c r="C148" t="n">
         <v>53.95999908447266</v>
@@ -4247,7 +4247,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>40.32558441162109</v>
+        <v>40.32559204101562</v>
       </c>
       <c r="C149" t="n">
         <v>51.61999893188477</v>
@@ -4276,7 +4276,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>39.16941452026367</v>
+        <v>39.16939926147461</v>
       </c>
       <c r="C150" t="n">
         <v>50.13999938964844</v>
@@ -4305,7 +4305,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>37.02893447875977</v>
+        <v>37.02892684936523</v>
       </c>
       <c r="C151" t="n">
         <v>47.40000152587891</v>
@@ -4363,7 +4363,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>38.37153625488281</v>
+        <v>38.37154006958008</v>
       </c>
       <c r="C153" t="n">
         <v>48.83000183105469</v>
@@ -4392,7 +4392,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>36.59558868408203</v>
+        <v>36.59558486938477</v>
       </c>
       <c r="C154" t="n">
         <v>46.56999969482422</v>
@@ -4450,7 +4450,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>35.12223434448242</v>
+        <v>35.12223815917969</v>
       </c>
       <c r="C156" t="n">
         <v>44.38999938964844</v>
@@ -4479,7 +4479,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>31.37186431884766</v>
+        <v>31.37185287475586</v>
       </c>
       <c r="C157" t="n">
         <v>39.65000152587891</v>
@@ -4537,7 +4537,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>33.45157623291016</v>
+        <v>33.45158767700195</v>
       </c>
       <c r="C159" t="n">
         <v>41.97999954223633</v>
@@ -4566,7 +4566,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>33.62688827514648</v>
+        <v>33.62688064575195</v>
       </c>
       <c r="C160" t="n">
         <v>42.20000076293945</v>
@@ -4595,7 +4595,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>38.69016647338867</v>
+        <v>38.6901741027832</v>
       </c>
       <c r="C161" t="n">
         <v>48.25</v>
@@ -4624,7 +4624,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>32.6280517578125</v>
+        <v>32.62804794311523</v>
       </c>
       <c r="C162" t="n">
         <v>40.68999862670898</v>
@@ -4653,7 +4653,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>35.12986755371094</v>
+        <v>35.12987518310547</v>
       </c>
       <c r="C163" t="n">
         <v>43.81000137329102</v>
@@ -4682,7 +4682,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>36.00993347167969</v>
+        <v>36.00992965698242</v>
       </c>
       <c r="C164" t="n">
         <v>44.56000137329102</v>
@@ -4711,7 +4711,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>33.52899551391602</v>
+        <v>33.52899932861328</v>
       </c>
       <c r="C165" t="n">
         <v>41.4900016784668</v>
@@ -4740,7 +4740,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>34.48258209228516</v>
+        <v>34.48257446289062</v>
       </c>
       <c r="C166" t="n">
         <v>42.66999816894531</v>
@@ -4769,7 +4769,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>37.49425888061523</v>
+        <v>37.4942626953125</v>
       </c>
       <c r="C167" t="n">
         <v>46.04999923706055</v>
@@ -4798,7 +4798,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>40.2869987487793</v>
+        <v>40.28698348999023</v>
       </c>
       <c r="C168" t="n">
         <v>49.47999954223633</v>
@@ -4827,7 +4827,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>41.62228393554688</v>
+        <v>41.62228775024414</v>
       </c>
       <c r="C169" t="n">
         <v>51.11999893188477</v>
@@ -4856,7 +4856,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>42.82973861694336</v>
+        <v>42.82974624633789</v>
       </c>
       <c r="C170" t="n">
         <v>52.2599983215332</v>
@@ -4885,7 +4885,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>36.90437698364258</v>
+        <v>36.90438842773438</v>
       </c>
       <c r="C171" t="n">
         <v>45.02999877929688</v>
@@ -4914,7 +4914,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>27.86473655700684</v>
+        <v>27.86473846435547</v>
       </c>
       <c r="C172" t="n">
         <v>34</v>
@@ -4943,7 +4943,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>32.59922409057617</v>
+        <v>32.59921264648438</v>
       </c>
       <c r="C173" t="n">
         <v>39.43000030517578</v>
@@ -5001,7 +5001,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>39.93260955810547</v>
+        <v>39.93259811401367</v>
       </c>
       <c r="C175" t="n">
         <v>48.29999923706055</v>
@@ -5030,7 +5030,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>40.69366073608398</v>
+        <v>40.69364929199219</v>
       </c>
       <c r="C176" t="n">
         <v>48.88000106811523</v>
@@ -5059,7 +5059,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>43.50757598876953</v>
+        <v>43.50758361816406</v>
       </c>
       <c r="C177" t="n">
         <v>52.2599983215332</v>
@@ -5088,7 +5088,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>40.25241470336914</v>
+        <v>40.25241851806641</v>
       </c>
       <c r="C178" t="n">
         <v>48.34999847412109</v>
@@ -5117,7 +5117,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>40.38303375244141</v>
+        <v>40.38304138183594</v>
       </c>
       <c r="C179" t="n">
         <v>48.15000152587891</v>
@@ -5146,7 +5146,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>51.85634613037109</v>
+        <v>51.85635375976562</v>
       </c>
       <c r="C180" t="n">
         <v>61.83000183105469</v>
@@ -5175,7 +5175,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>57.47558212280273</v>
+        <v>57.47557830810547</v>
       </c>
       <c r="C181" t="n">
         <v>68.52999877929688</v>
@@ -5233,7 +5233,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>64.80176544189453</v>
+        <v>64.80178070068359</v>
       </c>
       <c r="C183" t="n">
         <v>76.87000274658203</v>
@@ -5320,7 +5320,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>76.99701690673828</v>
+        <v>76.99702453613281</v>
       </c>
       <c r="C186" t="n">
         <v>90.94999694824219</v>
@@ -5349,7 +5349,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>77.62351226806641</v>
+        <v>77.62349700927734</v>
       </c>
       <c r="C187" t="n">
         <v>91.69000244140625</v>
@@ -5378,7 +5378,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>81.85176086425781</v>
+        <v>81.85173034667969</v>
       </c>
       <c r="C188" t="n">
         <v>95.98000335693359</v>
@@ -5407,7 +5407,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>89.05791473388672</v>
+        <v>89.05792236328125</v>
       </c>
       <c r="C189" t="n">
         <v>104.4300003051758</v>
@@ -5436,7 +5436,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>82.98598480224609</v>
+        <v>82.98599243164062</v>
       </c>
       <c r="C190" t="n">
         <v>97.30999755859375</v>
@@ -5465,7 +5465,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>88.25726318359375</v>
+        <v>88.25725555419922</v>
       </c>
       <c r="C191" t="n">
         <v>102.7799987792969</v>
@@ -5494,7 +5494,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>81.42201995849609</v>
+        <v>81.4219970703125</v>
       </c>
       <c r="C192" t="n">
         <v>94.81999969482422</v>
@@ -5523,7 +5523,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>84.29006195068359</v>
+        <v>84.29005432128906</v>
       </c>
       <c r="C193" t="n">
         <v>98.16000366210938</v>
@@ -5581,7 +5581,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>78.46147155761719</v>
+        <v>78.46146392822266</v>
       </c>
       <c r="C195" t="n">
         <v>90.73999786376953</v>
@@ -5610,7 +5610,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>75.57344055175781</v>
+        <v>75.57343292236328</v>
       </c>
       <c r="C196" t="n">
         <v>87.40000152587891</v>
@@ -5639,7 +5639,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>70.28337097167969</v>
+        <v>70.28338623046875</v>
       </c>
       <c r="C197" t="n">
         <v>80.58999633789062</v>
@@ -5668,7 +5668,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>75.12358093261719</v>
+        <v>75.12358856201172</v>
       </c>
       <c r="C198" t="n">
         <v>86.13999938964844</v>
@@ -5726,7 +5726,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>74.21600341796875</v>
+        <v>74.21601104736328</v>
       </c>
       <c r="C200" t="n">
         <v>84.30000305175781</v>
@@ -5755,7 +5755,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>75.02595520019531</v>
+        <v>75.02597808837891</v>
       </c>
       <c r="C201" t="n">
         <v>85.22000122070312</v>
@@ -5784,7 +5784,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>69.55879211425781</v>
+        <v>69.55881500244141</v>
       </c>
       <c r="C202" t="n">
         <v>79.01000213623047</v>
@@ -5813,7 +5813,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>73.04233551025391</v>
+        <v>73.04232788085938</v>
       </c>
       <c r="C203" t="n">
         <v>82.16999816894531</v>
@@ -5871,7 +5871,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>75.57574462890625</v>
+        <v>75.57575988769531</v>
       </c>
       <c r="C205" t="n">
         <v>85.01999664306641</v>
@@ -5900,7 +5900,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>87.21617126464844</v>
+        <v>87.21617889404297</v>
       </c>
       <c r="C206" t="n">
         <v>97.33000183105469</v>
@@ -5929,7 +5929,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>86.47241973876953</v>
+        <v>86.472412109375</v>
       </c>
       <c r="C207" t="n">
         <v>96.5</v>
@@ -5958,7 +5958,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>78.67646789550781</v>
+        <v>78.67647552490234</v>
       </c>
       <c r="C208" t="n">
         <v>87.80000305175781</v>
@@ -6016,7 +6016,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>73.89860534667969</v>
+        <v>73.89862823486328</v>
       </c>
       <c r="C210" t="n">
         <v>81.76000213623047</v>
@@ -6045,7 +6045,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>77.18862915039062</v>
+        <v>77.18862152099609</v>
       </c>
       <c r="C211" t="n">
         <v>85.40000152587891</v>
@@ -6074,7 +6074,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>83.52174377441406</v>
+        <v>83.521728515625</v>
       </c>
       <c r="C212" t="n">
         <v>91.55999755859375</v>
@@ -6103,7 +6103,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>77.67449951171875</v>
+        <v>77.67448425292969</v>
       </c>
       <c r="C213" t="n">
         <v>85.15000152587891</v>
@@ -6132,7 +6132,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>74.5</v>
+        <v>74.50001525878906</v>
       </c>
       <c r="C214" t="n">
         <v>81.66999816894531</v>
@@ -6161,7 +6161,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>65.39209747314453</v>
+        <v>65.39207458496094</v>
       </c>
       <c r="C215" t="n">
         <v>70.81999969482422</v>
@@ -6190,7 +6190,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>73.25906372070312</v>
+        <v>73.25908660888672</v>
       </c>
       <c r="C216" t="n">
         <v>79.33999633789062</v>
@@ -6219,7 +6219,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>86.10296630859375</v>
+        <v>86.10297393798828</v>
       </c>
       <c r="C217" t="n">
         <v>93.25</v>
@@ -6248,7 +6248,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>81.34268951416016</v>
+        <v>81.34270477294922</v>
       </c>
       <c r="C218" t="n">
         <v>87.23999786376953</v>
@@ -6277,7 +6277,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>80.22381591796875</v>
+        <v>80.22382354736328</v>
       </c>
       <c r="C219" t="n">
         <v>86.04000091552734</v>
@@ -6422,7 +6422,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>97.99607849121094</v>
+        <v>97.99606323242188</v>
       </c>
       <c r="C224" t="n">
         <v>103.2099990844727</v>
@@ -6480,7 +6480,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>98.97403717041016</v>
+        <v>98.97405242919922</v>
       </c>
       <c r="C226" t="n">
         <v>104.2399978637695</v>
@@ -6538,7 +6538,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>125.9493637084961</v>
+        <v>125.9493713378906</v>
       </c>
       <c r="C228" t="n">
         <v>131.6100006103516</v>
@@ -6596,7 +6596,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>133.3574981689453</v>
+        <v>133.3575134277344</v>
       </c>
       <c r="C230" t="n">
         <v>138.4299926757812</v>
@@ -6654,7 +6654,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>112.3948745727539</v>
+        <v>112.3948669433594</v>
       </c>
       <c r="C232" t="n">
         <v>116.6699981689453</v>
@@ -6683,7 +6683,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>112.0828094482422</v>
+        <v>112.0828170776367</v>
       </c>
       <c r="C233" t="n">
         <v>115.4199981689453</v>
@@ -6712,7 +6712,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>124.3282241821289</v>
+        <v>124.3282165527344</v>
       </c>
       <c r="C234" t="n">
         <v>128.0299987792969</v>
@@ -6741,7 +6741,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>136.7872619628906</v>
+        <v>136.7872772216797</v>
       </c>
       <c r="C235" t="n">
         <v>140.8600006103516</v>
@@ -6770,7 +6770,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>139.3020935058594</v>
+        <v>139.3021240234375</v>
       </c>
       <c r="C236" t="n">
         <v>142.4600067138672</v>
